--- a/data/raw/female_life_table_southeast_brazil_2025.xlsx
+++ b/data/raw/female_life_table_southeast_brazil_2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/Projeto IC - Vanessa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/projeto_longevidade/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29A58FD9-17FE-4660-9A83-0FAEE8F25C76}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AD68D43-06FD-4BC8-A5C0-C50F45CCBC5F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,31 +516,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>1.02961936387735E-2</v>
+        <v>1.0667380374314099E-2</v>
       </c>
       <c r="C2" s="4">
-        <v>8.0598921381836205E-2</v>
+        <v>8.1691691090743507E-2</v>
       </c>
       <c r="D2" s="4">
-        <v>1.01996404606136E-2</v>
+        <v>1.0563897030245699E-2</v>
       </c>
       <c r="E2" s="5">
         <v>100000</v>
       </c>
       <c r="F2" s="5">
-        <v>1019.96404606136</v>
+        <v>1056.3897030245701</v>
       </c>
       <c r="G2" s="5">
-        <v>99062.243955899394</v>
+        <v>99029.908558266397</v>
       </c>
       <c r="H2" s="6">
-        <v>0.98906576321333495</v>
+        <v>0.98867994820295901</v>
       </c>
       <c r="I2" s="5">
-        <v>8008111.5070036203</v>
+        <v>7969079.9126410298</v>
       </c>
       <c r="J2" s="7">
-        <v>80.081115070036205</v>
+        <v>79.690799126410298</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -548,31 +548,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>4.5600365779633597E-4</v>
+        <v>4.7116735266214502E-4</v>
       </c>
       <c r="C3" s="4">
-        <v>1.50739718020101</v>
+        <v>1.5068042899170699</v>
       </c>
       <c r="D3" s="4">
-        <v>1.82194374432962E-3</v>
+        <v>1.8824580637764299E-3</v>
       </c>
       <c r="E3" s="5">
-        <v>98980.035953938597</v>
+        <v>98943.610296975399</v>
       </c>
       <c r="F3" s="5">
-        <v>180.336057319801</v>
+        <v>186.25719706268899</v>
       </c>
       <c r="G3" s="5">
-        <v>395470.63765076798</v>
+        <v>395310.06554321299</v>
       </c>
       <c r="H3" s="6">
-        <v>0.99835916852879103</v>
+        <v>0.99829990295485305</v>
       </c>
       <c r="I3" s="5">
-        <v>7909049.2630477203</v>
+        <v>7870050.0040827701</v>
       </c>
       <c r="J3" s="7">
-        <v>79.905500001316199</v>
+        <v>79.540760443864102</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -580,31 +580,31 @@
         <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>2.0787300408654999E-4</v>
+        <v>2.1571422694353001E-4</v>
       </c>
       <c r="C4" s="4">
-        <v>2.3004060648346298</v>
+        <v>2.30198047467794</v>
       </c>
       <c r="D4" s="4">
-        <v>1.0387820842846401E-3</v>
+        <v>1.0779437701540001E-3</v>
       </c>
       <c r="E4" s="5">
-        <v>98799.699896618797</v>
+        <v>98757.353099912696</v>
       </c>
       <c r="F4" s="5">
-        <v>102.631358185317</v>
+        <v>106.454873530965</v>
       </c>
       <c r="G4" s="5">
-        <v>493721.43649097899</v>
+        <v>493499.54817221098</v>
       </c>
       <c r="H4" s="6">
-        <v>0.99908217150605505</v>
+        <v>0.99904610996259002</v>
       </c>
       <c r="I4" s="5">
-        <v>7513578.6253969604</v>
+        <v>7474739.9385395497</v>
       </c>
       <c r="J4" s="7">
-        <v>76.048597650184703</v>
+        <v>75.687933140303599</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -612,31 +612,31 @@
         <v>10</v>
       </c>
       <c r="B5" s="4">
-        <v>1.8388807420319E-4</v>
+        <v>1.9138624172154801E-4</v>
       </c>
       <c r="C5" s="4">
-        <v>2.6070223268288801</v>
+        <v>2.6082045168996499</v>
       </c>
       <c r="D5" s="4">
-        <v>9.1903595838142003E-4</v>
+        <v>9.5649336731397903E-4</v>
       </c>
       <c r="E5" s="5">
-        <v>98697.068538433494</v>
+        <v>98650.898226381803</v>
       </c>
       <c r="F5" s="5">
-        <v>90.706154973639102</v>
+        <v>94.358929833091693</v>
       </c>
       <c r="G5" s="5">
-        <v>493268.28488849697</v>
+        <v>493028.80386974401</v>
       </c>
       <c r="H5" s="6">
-        <v>0.99872780531597105</v>
+        <v>0.99867385144329701</v>
       </c>
       <c r="I5" s="5">
-        <v>7019857.1889059804</v>
+        <v>6981240.3903673403</v>
       </c>
       <c r="J5" s="7">
-        <v>71.125285612433203</v>
+        <v>70.767124434558696</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -644,31 +644,31 @@
         <v>15</v>
       </c>
       <c r="B6" s="4">
-        <v>3.4809428795644798E-4</v>
+        <v>3.6330767029392599E-4</v>
       </c>
       <c r="C6" s="4">
-        <v>2.71957119106666</v>
+        <v>2.7207410933188001</v>
       </c>
       <c r="D6" s="4">
-        <v>1.73909094201441E-3</v>
+        <v>1.8150353710581E-3</v>
       </c>
       <c r="E6" s="5">
-        <v>98606.362383459898</v>
+        <v>98556.539296548697</v>
       </c>
       <c r="F6" s="5">
-        <v>171.48543164607</v>
+        <v>178.88360487231699</v>
       </c>
       <c r="G6" s="5">
-        <v>492640.75159866101</v>
+        <v>492374.97443307901</v>
       </c>
       <c r="H6" s="6">
-        <v>0.99780418716947095</v>
+        <v>0.99770423536022501</v>
       </c>
       <c r="I6" s="5">
-        <v>6526588.9040174801</v>
+        <v>6488211.5864976002</v>
       </c>
       <c r="J6" s="7">
-        <v>66.188314285815693</v>
+        <v>65.832380406287299</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -676,31 +676,31 @@
         <v>20</v>
       </c>
       <c r="B7" s="4">
-        <v>5.2940299130727097E-4</v>
+        <v>5.5417688275345202E-4</v>
       </c>
       <c r="C7" s="4">
-        <v>2.6352710885282402</v>
+        <v>2.6355803927821202</v>
       </c>
       <c r="D7" s="4">
-        <v>2.6437053162343999E-3</v>
+        <v>2.7672584565058E-3</v>
       </c>
       <c r="E7" s="5">
-        <v>98434.8769518138</v>
+        <v>98377.655691676395</v>
       </c>
       <c r="F7" s="5">
-        <v>260.23280750038998</v>
+        <v>272.23639964401099</v>
       </c>
       <c r="G7" s="5">
-        <v>491559.00471545901</v>
+        <v>491244.59737726499</v>
       </c>
       <c r="H7" s="6">
-        <v>0.99700104209927498</v>
+        <v>0.99686247581381304</v>
       </c>
       <c r="I7" s="5">
-        <v>6033948.1524188202</v>
+        <v>5995836.6120645199</v>
       </c>
       <c r="J7" s="7">
-        <v>61.2988844936798</v>
+        <v>60.947138554063201</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -708,31 +708,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="4">
-        <v>6.6985993636428296E-4</v>
+        <v>7.00348246282808E-4</v>
       </c>
       <c r="C8" s="4">
-        <v>2.5985101880602999</v>
+        <v>2.5980171453425398</v>
       </c>
       <c r="D8" s="4">
-        <v>3.34392044469764E-3</v>
+        <v>3.49586040945508E-3</v>
       </c>
       <c r="E8" s="5">
-        <v>98174.644144313395</v>
+        <v>98105.419292032399</v>
       </c>
       <c r="F8" s="5">
-        <v>328.28819970508602</v>
+        <v>342.96285125600099</v>
       </c>
       <c r="G8" s="5">
-        <v>490084.83995459502</v>
+        <v>489703.30557165999</v>
       </c>
       <c r="H8" s="6">
-        <v>0.99622962533372195</v>
+        <v>0.996060496774273</v>
       </c>
       <c r="I8" s="5">
-        <v>5542389.1477033598</v>
+        <v>5504592.0146872504</v>
       </c>
       <c r="J8" s="7">
-        <v>56.454384897552899</v>
+        <v>56.108949479147803</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -740,31 +740,31 @@
         <v>30</v>
       </c>
       <c r="B9" s="4">
-        <v>8.5516757356184298E-4</v>
+        <v>8.9334218988927096E-4</v>
       </c>
       <c r="C9" s="4">
-        <v>2.61752118341203</v>
+        <v>2.6175185461207802</v>
       </c>
       <c r="D9" s="4">
-        <v>4.2671439093172701E-3</v>
+        <v>4.45722432157115E-3</v>
       </c>
       <c r="E9" s="5">
-        <v>97846.355944608295</v>
+        <v>97762.456440776397</v>
       </c>
       <c r="F9" s="5">
-        <v>417.52448181793397</v>
+        <v>435.74919858436601</v>
       </c>
       <c r="G9" s="5">
-        <v>488237.03648970398</v>
+        <v>487774.11781971197</v>
       </c>
       <c r="H9" s="6">
-        <v>0.99497884351280796</v>
+        <v>0.99475219226884404</v>
       </c>
       <c r="I9" s="5">
-        <v>5052304.3077487601</v>
+        <v>5014888.70911559</v>
       </c>
       <c r="J9" s="7">
-        <v>51.635078884377798</v>
+        <v>51.296672482381503</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -772,31 +772,31 @@
         <v>35</v>
       </c>
       <c r="B10" s="4">
-        <v>1.18763830493626E-3</v>
+        <v>1.2421513926428099E-3</v>
       </c>
       <c r="C10" s="4">
-        <v>2.6450908428535702</v>
+        <v>2.6453620106781401</v>
       </c>
       <c r="D10" s="4">
-        <v>5.92163002636321E-3</v>
+        <v>6.1926446118601196E-3</v>
       </c>
       <c r="E10" s="5">
-        <v>97428.831462790404</v>
+        <v>97326.707242192002</v>
       </c>
       <c r="F10" s="5">
-        <v>576.93749382352701</v>
+        <v>602.70970919344097</v>
       </c>
       <c r="G10" s="5">
-        <v>485785.521926646</v>
+        <v>485214.37303315999</v>
       </c>
       <c r="H10" s="6">
-        <v>0.99280585841582203</v>
+        <v>0.99247355596148901</v>
       </c>
       <c r="I10" s="5">
-        <v>4564067.2712590601</v>
+        <v>4527114.5912958803</v>
       </c>
       <c r="J10" s="7">
-        <v>46.845140219116203</v>
+        <v>46.514617822530603</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -804,31 +804,31 @@
         <v>40</v>
       </c>
       <c r="B11" s="4">
-        <v>1.7364704776065699E-3</v>
+        <v>1.81733943935824E-3</v>
       </c>
       <c r="C11" s="4">
-        <v>2.64919840580693</v>
+        <v>2.6489467014631201</v>
       </c>
       <c r="D11" s="4">
-        <v>8.6470542688400504E-3</v>
+        <v>9.0480379897522403E-3</v>
       </c>
       <c r="E11" s="5">
-        <v>96851.893968966906</v>
+        <v>96723.997532998503</v>
       </c>
       <c r="F11" s="5">
-        <v>837.48358318960504</v>
+        <v>875.16240419927601</v>
       </c>
       <c r="G11" s="5">
-        <v>482290.71210236201</v>
+        <v>481562.43420784501</v>
       </c>
       <c r="H11" s="6">
-        <v>0.98964295396871504</v>
+        <v>0.98916843125801102</v>
       </c>
       <c r="I11" s="5">
-        <v>4078281.7493324098</v>
+        <v>4041900.2182627199</v>
       </c>
       <c r="J11" s="7">
-        <v>42.108435697077603</v>
+        <v>41.787977351574803</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -836,31 +836,31 @@
         <v>45</v>
       </c>
       <c r="B12" s="4">
-        <v>2.4731280591372999E-3</v>
+        <v>2.5856125205192099E-3</v>
       </c>
       <c r="C12" s="4">
-        <v>2.64790241056195</v>
+        <v>2.6472010278036699</v>
       </c>
       <c r="D12" s="4">
-        <v>1.2294124897266501E-2</v>
+        <v>1.28498912339881E-2</v>
       </c>
       <c r="E12" s="5">
-        <v>96014.410385777301</v>
+        <v>95848.835128799299</v>
       </c>
       <c r="F12" s="5">
-        <v>1180.41315322014</v>
+        <v>1231.64710630954</v>
       </c>
       <c r="G12" s="5">
-        <v>477295.60499665601</v>
+        <v>476346.35759816301</v>
       </c>
       <c r="H12" s="6">
-        <v>0.98509471037280305</v>
+        <v>0.98443256211360897</v>
       </c>
       <c r="I12" s="5">
-        <v>3595991.0372300502</v>
+        <v>3560337.78405488</v>
       </c>
       <c r="J12" s="7">
-        <v>37.452618026624201</v>
+        <v>37.145342238855399</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -868,31 +868,31 @@
         <v>50</v>
       </c>
       <c r="B13" s="4">
-        <v>3.6201571744657601E-3</v>
+        <v>3.7802670062274898E-3</v>
       </c>
       <c r="C13" s="4">
-        <v>2.6566952760502698</v>
+        <v>2.65605424644566</v>
       </c>
       <c r="D13" s="4">
-        <v>1.79485261662738E-2</v>
+        <v>1.8735326162274701E-2</v>
       </c>
       <c r="E13" s="5">
-        <v>94833.9972325571</v>
+        <v>94617.188022489703</v>
       </c>
       <c r="F13" s="5">
-        <v>1702.1304807808899</v>
+        <v>1772.68387815861</v>
       </c>
       <c r="G13" s="5">
-        <v>470181.37576639297</v>
+        <v>468930.86526384403</v>
       </c>
       <c r="H13" s="6">
-        <v>0.97795431063709304</v>
+        <v>0.97699446854897498</v>
       </c>
       <c r="I13" s="5">
-        <v>3118695.4322334002</v>
+        <v>3083991.4264567099</v>
       </c>
       <c r="J13" s="7">
-        <v>32.885837603001796</v>
+        <v>32.594410074030897</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -900,31 +900,31 @@
         <v>55</v>
       </c>
       <c r="B14" s="4">
-        <v>5.4402372219593698E-3</v>
+        <v>5.6792857962944896E-3</v>
       </c>
       <c r="C14" s="4">
-        <v>2.6640364531480598</v>
+        <v>2.66339883398462</v>
       </c>
       <c r="D14" s="4">
-        <v>2.6859845927604601E-2</v>
+        <v>2.80245370465389E-2</v>
       </c>
       <c r="E14" s="5">
-        <v>93131.866751776193</v>
+        <v>92844.504144331106</v>
       </c>
       <c r="F14" s="5">
-        <v>2501.50759190292</v>
+        <v>2601.9242459603402</v>
       </c>
       <c r="G14" s="5">
-        <v>459815.90321202303</v>
+        <v>458142.86149466102</v>
       </c>
       <c r="H14" s="6">
-        <v>0.96656439264990501</v>
+        <v>0.96512181089167703</v>
       </c>
       <c r="I14" s="5">
-        <v>2648514.0564669999</v>
+        <v>2615060.5611928701</v>
       </c>
       <c r="J14" s="7">
-        <v>28.438322443660098</v>
+        <v>28.166024314456301</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -932,31 +932,31 @@
         <v>60</v>
       </c>
       <c r="B15" s="4">
-        <v>8.4005299285044594E-3</v>
+        <v>8.76618674231169E-3</v>
       </c>
       <c r="C15" s="4">
-        <v>2.6670657201229502</v>
+        <v>2.6653707661373298</v>
       </c>
       <c r="D15" s="4">
-        <v>4.1195308750427498E-2</v>
+        <v>4.2951889118008499E-2</v>
       </c>
       <c r="E15" s="5">
-        <v>90630.359159873304</v>
+        <v>90242.579898370794</v>
       </c>
       <c r="F15" s="5">
-        <v>3733.5456277531198</v>
+        <v>3876.0892855178499</v>
       </c>
       <c r="G15" s="5">
-        <v>444441.67921889602</v>
+        <v>442163.66813282197</v>
       </c>
       <c r="H15" s="6">
-        <v>0.94816943537767395</v>
+        <v>0.946077468722064</v>
       </c>
       <c r="I15" s="5">
-        <v>2188698.1532549802</v>
+        <v>2156917.6996982102</v>
       </c>
       <c r="J15" s="7">
-        <v>24.1497239285357</v>
+        <v>23.901330193876099</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -964,31 +964,31 @@
         <v>65</v>
       </c>
       <c r="B16" s="4">
-        <v>1.3193752508866299E-2</v>
+        <v>1.3711940596522299E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>2.64780142496967</v>
+        <v>2.6444589197630299</v>
       </c>
       <c r="D16" s="4">
-        <v>6.3983090465881201E-2</v>
+        <v>6.6414575978674797E-2</v>
       </c>
       <c r="E16" s="5">
-        <v>86896.813532120199</v>
+        <v>86366.490612852896</v>
       </c>
       <c r="F16" s="5">
-        <v>5559.9266814224402</v>
+        <v>5735.9938528188204</v>
       </c>
       <c r="G16" s="5">
-        <v>421406.01604328601</v>
+        <v>418321.08390796301</v>
       </c>
       <c r="H16" s="6">
-        <v>0.92289006409955299</v>
+        <v>0.92026204972214898</v>
       </c>
       <c r="I16" s="5">
-        <v>1744256.4740360901</v>
+        <v>1714754.0315653901</v>
       </c>
       <c r="J16" s="7">
-        <v>20.0727322802388</v>
+        <v>19.854390509531701</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -996,31 +996,31 @@
         <v>70</v>
       </c>
       <c r="B17" s="4">
-        <v>1.9485666724556601E-2</v>
+        <v>2.0114161628699199E-2</v>
       </c>
       <c r="C17" s="4">
-        <v>2.6547184278217801</v>
+        <v>2.6511840662328399</v>
       </c>
       <c r="D17" s="4">
-        <v>9.3170499996073602E-2</v>
+        <v>9.6033745381579202E-2</v>
       </c>
       <c r="E17" s="5">
-        <v>81336.886850697803</v>
+        <v>80630.496760034104</v>
       </c>
       <c r="F17" s="5">
-        <v>7578.19841600358</v>
+        <v>7743.2485958433699</v>
       </c>
       <c r="G17" s="5">
-        <v>388911.425158125</v>
+        <v>384965.01811913302</v>
       </c>
       <c r="H17" s="6">
-        <v>0.879025787047091</v>
+        <v>0.87563800453247997</v>
       </c>
       <c r="I17" s="5">
-        <v>1322850.4579928</v>
+        <v>1296432.9476574201</v>
       </c>
       <c r="J17" s="7">
-        <v>16.263844231228401</v>
+        <v>16.078692303183502</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1028,31 +1028,31 @@
         <v>75</v>
       </c>
       <c r="B18" s="4">
-        <v>3.3691599846102399E-2</v>
+        <v>3.4642878015282798E-2</v>
       </c>
       <c r="C18" s="4">
-        <v>2.6618801678417201</v>
+        <v>2.6582647383840698</v>
       </c>
       <c r="D18" s="4">
-        <v>0.15615675147978</v>
+        <v>0.16021688366650899</v>
       </c>
       <c r="E18" s="5">
-        <v>73758.688434694195</v>
+        <v>72887.248164190707</v>
       </c>
       <c r="F18" s="5">
-        <v>11517.917179371099</v>
+        <v>11677.767759894101</v>
       </c>
       <c r="G18" s="5">
-        <v>341863.171591227</v>
+        <v>337090.000280648</v>
       </c>
       <c r="H18" s="6">
-        <v>0.79729606504738104</v>
+        <v>0.79264230557985604</v>
       </c>
       <c r="I18" s="5">
-        <v>933939.032834674</v>
+        <v>911467.92953829095</v>
       </c>
       <c r="J18" s="7">
-        <v>12.6620883946653</v>
+        <v>12.5051768655754</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1060,31 +1060,31 @@
         <v>80</v>
       </c>
       <c r="B19" s="4">
-        <v>5.9359962055400201E-2</v>
+        <v>6.0795978884579799E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>2.61193768806399</v>
+        <v>2.6080300194322601</v>
       </c>
       <c r="D19" s="4">
-        <v>0.25995045815734802</v>
+        <v>0.26538677702029601</v>
       </c>
       <c r="E19" s="5">
-        <v>62240.771255323103</v>
+        <v>61209.480404296599</v>
       </c>
       <c r="F19" s="5">
-        <v>16179.517003887901</v>
+        <v>16244.186727583199</v>
       </c>
       <c r="G19" s="5">
-        <v>272566.16149430303</v>
+        <v>267191.795010367</v>
       </c>
       <c r="H19" s="6">
-        <v>0.67191667391818199</v>
+        <v>0.66550015422861497</v>
       </c>
       <c r="I19" s="5">
-        <v>592075.86124344706</v>
+        <v>574377.92925764294</v>
       </c>
       <c r="J19" s="7">
-        <v>9.5126690961884499</v>
+        <v>9.3838066499470596</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1092,31 +1092,31 @@
         <v>85</v>
       </c>
       <c r="B20" s="4">
-        <v>0.104391584798501</v>
+        <v>0.10686817290292901</v>
       </c>
       <c r="C20" s="4">
-        <v>2.5330372292012799</v>
+        <v>2.5261506685926598</v>
       </c>
       <c r="D20" s="4">
-        <v>0.41506593112699303</v>
+        <v>0.42261239279381702</v>
       </c>
       <c r="E20" s="5">
-        <v>46061.254251435203</v>
+        <v>44965.293676713402</v>
       </c>
       <c r="F20" s="5">
-        <v>19118.457384749101</v>
+        <v>19002.8903533925</v>
       </c>
       <c r="G20" s="5">
-        <v>183141.74865389799</v>
+        <v>177816.18078801999</v>
       </c>
       <c r="H20" s="6">
-        <v>0.42680379094065701</v>
+        <v>0.42114515935513203</v>
       </c>
       <c r="I20" s="5">
-        <v>319509.69974914403</v>
+        <v>307186.134247276</v>
       </c>
       <c r="J20" s="7">
-        <v>6.9366261284382702</v>
+        <v>6.8316274426194097</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1124,31 +1124,31 @@
         <v>90</v>
       </c>
       <c r="B21" s="4">
-        <v>0.19757425883643301</v>
+        <v>0.200683409316503</v>
       </c>
       <c r="C21" s="4">
-        <v>5.0613880871388099</v>
+        <v>4.9829729493127903</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
       <c r="E21" s="5">
-        <v>26942.796866686102</v>
+        <v>25962.403323320799</v>
       </c>
       <c r="F21" s="5">
-        <v>26942.796866686102</v>
+        <v>25962.403323320799</v>
       </c>
       <c r="G21" s="5">
-        <v>136367.95109524601</v>
+        <v>129369.95345925599</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
       </c>
       <c r="I21" s="5">
-        <v>136367.95109524601</v>
+        <v>129369.95345925599</v>
       </c>
       <c r="J21" s="7">
-        <v>5.0613880871388099</v>
+        <v>4.9829729493127903</v>
       </c>
     </row>
   </sheetData>
